--- a/results/tables/MAIN TABLE/yelp_train/Comparsion_yelp.xlsx
+++ b/results/tables/MAIN TABLE/yelp_train/Comparsion_yelp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SEM-6\ELECTIVES\DEPARTMENT-ELECTIVES\Recommendation Systems\RS-Project\results\tables\MAIN TABLE\yelp_train\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB95623-7AB9-4AF1-B004-5416401ED8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF0DE64-A0A2-412E-8264-DCEA3BFCEE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,12 +30,6 @@
     <t>Layers</t>
   </si>
   <si>
-    <t>Paper Recall@20</t>
-  </si>
-  <si>
-    <t>Paper NDCG@20</t>
-  </si>
-  <si>
     <t>1 Layer</t>
   </si>
   <si>
@@ -48,10 +42,16 @@
     <t>4 Layers</t>
   </si>
   <si>
-    <t>My Recall@20</t>
-  </si>
-  <si>
-    <t>My NDCG@20</t>
+    <t>Paper Recall@20(test set)</t>
+  </si>
+  <si>
+    <t>Paper NDCG@20(test set)</t>
+  </si>
+  <si>
+    <t>My Recall@20(train set)</t>
+  </si>
+  <si>
+    <t>My NDCG@20(train set)</t>
   </si>
 </sst>
 </file>
@@ -386,10 +386,10 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.88671875" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" customWidth="1"/>
-    <col min="4" max="4" width="11.21875" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.21875" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -397,13 +397,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -411,7 +411,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2">
         <v>6.3100000000000003E-2</v>
@@ -428,7 +428,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2">
         <v>6.2700000000000006E-2</v>
@@ -445,7 +445,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2">
         <v>6.3899999999999998E-2</v>
@@ -462,7 +462,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2">
         <v>6.4899999999999999E-2</v>
